--- a/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
+++ b/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>5</v>
@@ -663,7 +663,7 @@
         <v>1960</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>2024</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>10</v>
@@ -831,7 +831,7 @@
         <v>1960</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>2025</v>

--- a/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
+++ b/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
         <v>1960</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>2025</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>1960</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2025</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>10</v>
@@ -831,7 +831,7 @@
         <v>1960</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>2025</v>

--- a/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
+++ b/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
         <v>1960</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>2025</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>1960</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2025</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>10</v>
@@ -831,7 +831,7 @@
         <v>1960</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>2025</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>9</v>
@@ -999,7 +999,7 @@
         <v>1960</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>2025</v>

--- a/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
+++ b/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
         <v>1960</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>2025</v>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
@@ -915,7 +915,7 @@
         <v>1960</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>2025</v>

--- a/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
+++ b/assets/data/world-bank/catalog/catalogo_dataset_web_ove_banco_mundial.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>5</v>
@@ -663,7 +663,7 @@
         <v>1960</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>2024</v>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
         <v>1960</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>2025</v>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
@@ -915,7 +915,7 @@
         <v>1960</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>2025</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>9</v>
@@ -999,7 +999,7 @@
         <v>1960</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>2025</v>
